--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2019.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2019.xlsx
@@ -2089,7 +2089,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:44</t>
+    <t xml:space="preserve">2026-09-07 12:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2019.xlsx
@@ -2089,7 +2089,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:50</t>
+    <t xml:space="preserve">2026-09-08 10:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
